--- a/SOT_results/SOT_30deg.xlsx
+++ b/SOT_results/SOT_30deg.xlsx
@@ -152,7 +152,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>30° 模型数据（52点）</a:t>
+              <a:t>30° 模型数据（角度相关形状，52点）</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -181,7 +181,7 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Sheet1'!$A$2:$A$53</f>
+              <f>'Sheet1'!$A$2:$A$27</f>
             </numRef>
           </xVal>
           <yVal>
@@ -625,7 +625,7 @@
         <v>-0.035</v>
       </c>
       <c r="B2" t="n">
-        <v>7.577975761335487</v>
+        <v>8.366266926306173</v>
       </c>
     </row>
     <row r="3">
@@ -633,7 +633,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B3" t="n">
-        <v>7.488683185966928</v>
+        <v>7.783083060659582</v>
       </c>
     </row>
     <row r="4">
@@ -641,7 +641,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B4" t="n">
-        <v>7.482361587710758</v>
+        <v>7.32091435164443</v>
       </c>
     </row>
     <row r="5">
@@ -649,7 +649,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B5" t="n">
-        <v>7.480781188146703</v>
+        <v>7.372657372439897</v>
       </c>
     </row>
     <row r="6">
@@ -657,7 +657,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B6" t="n">
-        <v>7.483151787492768</v>
+        <v>7.47025543984111</v>
       </c>
     </row>
     <row r="7">
@@ -665,7 +665,7 @@
         <v>-0.021</v>
       </c>
       <c r="B7" t="n">
-        <v>7.479200788582665</v>
+        <v>7.483188588592592</v>
       </c>
     </row>
     <row r="8">
@@ -673,7 +673,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B8" t="n">
-        <v>7.477620389018609</v>
+        <v>7.439524860393856</v>
       </c>
     </row>
     <row r="9">
@@ -681,7 +681,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B9" t="n">
-        <v>7.48710278640289</v>
+        <v>7.43845302201026</v>
       </c>
     </row>
     <row r="10">
@@ -689,7 +689,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B10" t="n">
-        <v>7.479200788582665</v>
+        <v>7.436560836277589</v>
       </c>
     </row>
     <row r="11">
@@ -697,7 +697,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B11" t="n">
-        <v>7.498165583351208</v>
+        <v>7.42725721413388</v>
       </c>
     </row>
     <row r="12">
@@ -705,7 +705,7 @@
         <v>-0.007</v>
       </c>
       <c r="B12" t="n">
-        <v>7.491053785312993</v>
+        <v>7.421888261011556</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B13" t="n">
-        <v>7.483151787492768</v>
+        <v>7.425491227348444</v>
       </c>
     </row>
     <row r="14">
@@ -721,7 +721,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B14" t="n">
-        <v>7.487892986184917</v>
+        <v>7.422663686362126</v>
       </c>
     </row>
     <row r="15">
@@ -729,7 +729,7 @@
         <v>0.0014</v>
       </c>
       <c r="B15" t="n">
-        <v>7.486312586620862</v>
+        <v>7.420630092095929</v>
       </c>
     </row>
     <row r="16">
@@ -737,7 +737,7 @@
         <v>0.0042</v>
       </c>
       <c r="B16" t="n">
-        <v>7.496585183787153</v>
+        <v>7.418968786397502</v>
       </c>
     </row>
     <row r="17">
@@ -745,7 +745,7 @@
         <v>0.007</v>
       </c>
       <c r="B17" t="n">
-        <v>7.50290678204334</v>
+        <v>7.712825155392096</v>
       </c>
     </row>
     <row r="18">
@@ -753,7 +753,7 @@
         <v>0.0098</v>
       </c>
       <c r="B18" t="n">
-        <v>7.496585183787153</v>
+        <v>8.219359526865805</v>
       </c>
     </row>
     <row r="19">
@@ -761,7 +761,7 @@
         <v>0.0126</v>
       </c>
       <c r="B19" t="n">
-        <v>7.502116582261312</v>
+        <v>8.521333388293762</v>
       </c>
     </row>
     <row r="20">
@@ -769,7 +769,7 @@
         <v>0.0154</v>
       </c>
       <c r="B20" t="n">
-        <v>7.506067581171433</v>
+        <v>8.533763513239384</v>
       </c>
     </row>
     <row r="21">
@@ -777,7 +777,7 @@
         <v>0.0182</v>
       </c>
       <c r="B21" t="n">
-        <v>7.500536182697275</v>
+        <v>8.515531962378061</v>
       </c>
     </row>
     <row r="22">
@@ -785,7 +785,7 @@
         <v>0.021</v>
       </c>
       <c r="B22" t="n">
-        <v>7.506857780953461</v>
+        <v>8.450732587372531</v>
       </c>
     </row>
     <row r="23">
@@ -793,7 +793,7 @@
         <v>0.0238</v>
       </c>
       <c r="B23" t="n">
-        <v>7.510808779863565</v>
+        <v>8.306671341373042</v>
       </c>
     </row>
     <row r="24">
@@ -801,7 +801,7 @@
         <v>0.0266</v>
       </c>
       <c r="B24" t="n">
-        <v>7.526612775504015</v>
+        <v>7.754353945805643</v>
       </c>
     </row>
     <row r="25">
@@ -809,7 +809,7 @@
         <v>0.0294</v>
       </c>
       <c r="B25" t="n">
-        <v>7.59694055610403</v>
+        <v>8.144894088974961</v>
       </c>
     </row>
     <row r="26">
@@ -817,7 +817,7 @@
         <v>0.0322</v>
       </c>
       <c r="B26" t="n">
-        <v>7.892475274580483</v>
+        <v>8.44039026402805</v>
       </c>
     </row>
     <row r="27">
@@ -825,7 +825,7 @@
         <v>0.035</v>
       </c>
       <c r="B27" t="n">
-        <v>8.2291003817221</v>
+        <v>8.144906434758418</v>
       </c>
     </row>
     <row r="28">
@@ -833,7 +833,7 @@
         <v>0.035</v>
       </c>
       <c r="B28" t="n">
-        <v>8.100297817252418</v>
+        <v>9.169671254739878</v>
       </c>
     </row>
     <row r="29">
@@ -841,7 +841,7 @@
         <v>0.0322</v>
       </c>
       <c r="B29" t="n">
-        <v>8.162723600032207</v>
+        <v>9.300103839809365</v>
       </c>
     </row>
     <row r="30">
@@ -849,7 +849,7 @@
         <v>0.0294</v>
       </c>
       <c r="B30" t="n">
-        <v>8.180898195018722</v>
+        <v>9.106285230180562</v>
       </c>
     </row>
     <row r="31">
@@ -857,7 +857,7 @@
         <v>0.0266</v>
       </c>
       <c r="B31" t="n">
-        <v>8.222778783465914</v>
+        <v>9.176631280010083</v>
       </c>
     </row>
     <row r="32">
@@ -865,7 +865,7 @@
         <v>0.0238</v>
       </c>
       <c r="B32" t="n">
-        <v>8.21961798433782</v>
+        <v>9.213915598172079</v>
       </c>
     </row>
     <row r="33">
@@ -873,7 +873,7 @@
         <v>0.021</v>
       </c>
       <c r="B33" t="n">
-        <v>8.222778783465914</v>
+        <v>8.997547827513923</v>
       </c>
     </row>
     <row r="34">
@@ -881,7 +881,7 @@
         <v>0.0182</v>
       </c>
       <c r="B34" t="n">
-        <v>8.239372978888392</v>
+        <v>8.328898843788675</v>
       </c>
     </row>
     <row r="35">
@@ -889,7 +889,7 @@
         <v>0.0154</v>
       </c>
       <c r="B35" t="n">
-        <v>8.233051380632205</v>
+        <v>8.217093009150146</v>
       </c>
     </row>
     <row r="36">
@@ -897,7 +897,7 @@
         <v>0.0126</v>
       </c>
       <c r="B36" t="n">
-        <v>8.244114177580522</v>
+        <v>8.214084133468713</v>
       </c>
     </row>
     <row r="37">
@@ -905,7 +905,7 @@
         <v>0.0098</v>
       </c>
       <c r="B37" t="n">
-        <v>8.259127973438963</v>
+        <v>8.195276175100046</v>
       </c>
     </row>
     <row r="38">
@@ -913,7 +913,7 @@
         <v>0.007</v>
       </c>
       <c r="B38" t="n">
-        <v>8.242533778016485</v>
+        <v>8.191986499258075</v>
       </c>
     </row>
     <row r="39">
@@ -921,7 +921,7 @@
         <v>0.0042</v>
       </c>
       <c r="B39" t="n">
-        <v>8.253596574964803</v>
+        <v>8.189133967719497</v>
       </c>
     </row>
     <row r="40">
@@ -929,7 +929,7 @@
         <v>0.0014</v>
       </c>
       <c r="B40" t="n">
-        <v>8.259127973438963</v>
+        <v>8.192370324294622</v>
       </c>
     </row>
     <row r="41">
@@ -937,7 +937,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B41" t="n">
-        <v>8.293896763847956</v>
+        <v>8.188708512347855</v>
       </c>
     </row>
     <row r="42">
@@ -945,7 +945,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B42" t="n">
-        <v>8.259127973438963</v>
+        <v>8.182470105518634</v>
       </c>
     </row>
     <row r="43">
@@ -953,7 +953,7 @@
         <v>-0.007</v>
       </c>
       <c r="B43" t="n">
-        <v>8.263869172131095</v>
+        <v>8.180201707416495</v>
       </c>
     </row>
     <row r="44">
@@ -961,7 +961,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B44" t="n">
-        <v>8.265449571695132</v>
+        <v>8.170769637729297</v>
       </c>
     </row>
     <row r="45">
@@ -969,7 +969,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B45" t="n">
-        <v>8.263869172131095</v>
+        <v>8.261370299826801</v>
       </c>
     </row>
     <row r="46">
@@ -977,7 +977,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B46" t="n">
-        <v>8.265449571695132</v>
+        <v>8.436582548855364</v>
       </c>
     </row>
     <row r="47">
@@ -985,7 +985,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B47" t="n">
-        <v>8.261498572785028</v>
+        <v>8.563203879004737</v>
       </c>
     </row>
     <row r="48">
@@ -993,7 +993,7 @@
         <v>-0.021</v>
       </c>
       <c r="B48" t="n">
-        <v>8.259918173220973</v>
+        <v>8.612640344994293</v>
       </c>
     </row>
     <row r="49">
@@ -1001,7 +1001,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B49" t="n">
-        <v>8.264659371913122</v>
+        <v>8.397341929105288</v>
       </c>
     </row>
     <row r="50">
@@ -1009,7 +1009,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B50" t="n">
-        <v>8.248855376272672</v>
+        <v>8.187604339112557</v>
       </c>
     </row>
     <row r="51">
@@ -1017,7 +1017,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B51" t="n">
-        <v>8.169835398070404</v>
+        <v>8.709972511140437</v>
       </c>
     </row>
     <row r="52">
@@ -1025,7 +1025,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B52" t="n">
-        <v>7.751819713380455</v>
+        <v>9.215041836348</v>
       </c>
     </row>
     <row r="53">
@@ -1033,7 +1033,7 @@
         <v>-0.035</v>
       </c>
       <c r="B53" t="n">
-        <v>7.314839233921961</v>
+        <v>9.338333271919506</v>
       </c>
     </row>
   </sheetData>
@@ -1074,11 +1074,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1144,84 +1144,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>电阻单位</t>
+          <t>翻转幅度A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>沿用原始文件数值；原始文件未注明纵轴单位</t>
+          <t>0.7653084889（保持前次角度模型）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>翻转幅度A</t>
+          <t>曲线形状</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.7653084889（按前次分析的平台差模型）</t>
+          <t>角度相关形状模板：0°/45°/75°实测回线归一化后按角度混合</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>中心基线</t>
+          <t>形状插值</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7.876473729（由已测角度基线保形插值，仅用于保持绘图尺度）</t>
+          <t>0°→45°线性混合</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>曲线形状</t>
+          <t>纵轴单位</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>复用165°实测回线的两支路形状，按目标角度A缩放；未添加随机噪声</t>
+          <t>原始文件未注明，保留原始数值尺度</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>模型规律</t>
+          <t>实测区分</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0–90°单峰角度依赖；采用0°/45°/75°/90°实测幅度锚点的保形插值</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>实测区分</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>本文件不是该角度的实测记录；15°、30°、60°原始文件夹无实测数据，0°和45°文件也已按52点序列重新模型化</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>输入模板</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>165度.xlsx（用户上传）</t>
+          <t>本文件为模型生成数据；15°、30°、60°无原始OPJU，0°/45°为统一点数并按实测模板生成</t>
         </is>
       </c>
     </row>

--- a/SOT_results/SOT_30deg.xlsx
+++ b/SOT_results/SOT_30deg.xlsx
@@ -152,7 +152,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>30° 模型数据（角度相关形状，52点）</a:t>
+              <a:t>30° 标准双支路SOT模型（52点）</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -625,7 +625,7 @@
         <v>-0.035</v>
       </c>
       <c r="B2" t="n">
-        <v>8.366266926306173</v>
+        <v>7.49381975555</v>
       </c>
     </row>
     <row r="3">
@@ -633,7 +633,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B3" t="n">
-        <v>7.783083060659582</v>
+        <v>7.493819755550001</v>
       </c>
     </row>
     <row r="4">
@@ -641,7 +641,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B4" t="n">
-        <v>7.32091435164443</v>
+        <v>7.493819755550004</v>
       </c>
     </row>
     <row r="5">
@@ -649,7 +649,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B5" t="n">
-        <v>7.372657372439897</v>
+        <v>7.493819755550022</v>
       </c>
     </row>
     <row r="6">
@@ -657,7 +657,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B6" t="n">
-        <v>7.47025543984111</v>
+        <v>7.493819755550114</v>
       </c>
     </row>
     <row r="7">
@@ -665,7 +665,7 @@
         <v>-0.021</v>
       </c>
       <c r="B7" t="n">
-        <v>7.483188588592592</v>
+        <v>7.493819755550594</v>
       </c>
     </row>
     <row r="8">
@@ -673,7 +673,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B8" t="n">
-        <v>7.439524860393856</v>
+        <v>7.493819755553086</v>
       </c>
     </row>
     <row r="9">
@@ -681,7 +681,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B9" t="n">
-        <v>7.43845302201026</v>
+        <v>7.493819755566025</v>
       </c>
     </row>
     <row r="10">
@@ -689,7 +689,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B10" t="n">
-        <v>7.436560836277589</v>
+        <v>7.493819755633199</v>
       </c>
     </row>
     <row r="11">
@@ -697,7 +697,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B11" t="n">
-        <v>7.42725721413388</v>
+        <v>7.493819755981944</v>
       </c>
     </row>
     <row r="12">
@@ -705,7 +705,7 @@
         <v>-0.007</v>
       </c>
       <c r="B12" t="n">
-        <v>7.421888261011556</v>
+        <v>7.493819757792517</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B13" t="n">
-        <v>7.425491227348444</v>
+        <v>7.493819767192449</v>
       </c>
     </row>
     <row r="14">
@@ -721,7 +721,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B14" t="n">
-        <v>7.422663686362126</v>
+        <v>7.493819815993961</v>
       </c>
     </row>
     <row r="15">
@@ -729,7 +729,7 @@
         <v>0.0014</v>
       </c>
       <c r="B15" t="n">
-        <v>7.420630092095929</v>
+        <v>7.493820069356063</v>
       </c>
     </row>
     <row r="16">
@@ -737,7 +737,7 @@
         <v>0.0042</v>
       </c>
       <c r="B16" t="n">
-        <v>7.418968786397502</v>
+        <v>7.493821384730269</v>
       </c>
     </row>
     <row r="17">
@@ -745,7 +745,7 @@
         <v>0.007</v>
       </c>
       <c r="B17" t="n">
-        <v>7.712825155392096</v>
+        <v>7.493828213669662</v>
       </c>
     </row>
     <row r="18">
@@ -753,7 +753,7 @@
         <v>0.0098</v>
       </c>
       <c r="B18" t="n">
-        <v>8.219359526865805</v>
+        <v>7.493863665431471</v>
       </c>
     </row>
     <row r="19">
@@ -761,7 +761,7 @@
         <v>0.0126</v>
       </c>
       <c r="B19" t="n">
-        <v>8.521333388293762</v>
+        <v>7.494047667127988</v>
       </c>
     </row>
     <row r="20">
@@ -769,7 +769,7 @@
         <v>0.0154</v>
       </c>
       <c r="B20" t="n">
-        <v>8.533763513239384</v>
+        <v>7.495001526078109</v>
       </c>
     </row>
     <row r="21">
@@ -777,7 +777,7 @@
         <v>0.0182</v>
       </c>
       <c r="B21" t="n">
-        <v>8.515531962378061</v>
+        <v>7.499915681933166</v>
       </c>
     </row>
     <row r="22">
@@ -785,7 +785,7 @@
         <v>0.021</v>
       </c>
       <c r="B22" t="n">
-        <v>8.450732587372531</v>
+        <v>7.524445369465496</v>
       </c>
     </row>
     <row r="23">
@@ -793,7 +793,7 @@
         <v>0.0238</v>
       </c>
       <c r="B23" t="n">
-        <v>8.306671341373042</v>
+        <v>7.629978997786136</v>
       </c>
     </row>
     <row r="24">
@@ -801,7 +801,7 @@
         <v>0.0266</v>
       </c>
       <c r="B24" t="n">
-        <v>7.754353945805643</v>
+        <v>7.898741373873175</v>
       </c>
     </row>
     <row r="25">
@@ -809,7 +809,7 @@
         <v>0.0294</v>
       </c>
       <c r="B25" t="n">
-        <v>8.144894088974961</v>
+        <v>8.147130508230694</v>
       </c>
     </row>
     <row r="26">
@@ -817,7 +817,7 @@
         <v>0.0322</v>
       </c>
       <c r="B26" t="n">
-        <v>8.44039026402805</v>
+        <v>8.23466530959443</v>
       </c>
     </row>
     <row r="27">
@@ -825,7 +825,7 @@
         <v>0.035</v>
       </c>
       <c r="B27" t="n">
-        <v>8.144906434758418</v>
+        <v>8.254291474969587</v>
       </c>
     </row>
     <row r="28">
@@ -833,7 +833,7 @@
         <v>0.035</v>
       </c>
       <c r="B28" t="n">
-        <v>9.169671254739878</v>
+        <v>8.25912824445</v>
       </c>
     </row>
     <row r="29">
@@ -841,7 +841,7 @@
         <v>0.0322</v>
       </c>
       <c r="B29" t="n">
-        <v>9.300103839809365</v>
+        <v>8.259128244449998</v>
       </c>
     </row>
     <row r="30">
@@ -849,7 +849,7 @@
         <v>0.0294</v>
       </c>
       <c r="B30" t="n">
-        <v>9.106285230180562</v>
+        <v>8.259128244449995</v>
       </c>
     </row>
     <row r="31">
@@ -857,7 +857,7 @@
         <v>0.0266</v>
       </c>
       <c r="B31" t="n">
-        <v>9.176631280010083</v>
+        <v>8.259128244449977</v>
       </c>
     </row>
     <row r="32">
@@ -865,7 +865,7 @@
         <v>0.0238</v>
       </c>
       <c r="B32" t="n">
-        <v>9.213915598172079</v>
+        <v>8.259128244449885</v>
       </c>
     </row>
     <row r="33">
@@ -873,7 +873,7 @@
         <v>0.021</v>
       </c>
       <c r="B33" t="n">
-        <v>8.997547827513923</v>
+        <v>8.259128244449405</v>
       </c>
     </row>
     <row r="34">
@@ -881,7 +881,7 @@
         <v>0.0182</v>
       </c>
       <c r="B34" t="n">
-        <v>8.328898843788675</v>
+        <v>8.259128244446913</v>
       </c>
     </row>
     <row r="35">
@@ -889,7 +889,7 @@
         <v>0.0154</v>
       </c>
       <c r="B35" t="n">
-        <v>8.217093009150146</v>
+        <v>8.259128244433974</v>
       </c>
     </row>
     <row r="36">
@@ -897,7 +897,7 @@
         <v>0.0126</v>
       </c>
       <c r="B36" t="n">
-        <v>8.214084133468713</v>
+        <v>8.259128244366801</v>
       </c>
     </row>
     <row r="37">
@@ -905,7 +905,7 @@
         <v>0.0098</v>
       </c>
       <c r="B37" t="n">
-        <v>8.195276175100046</v>
+        <v>8.259128244018056</v>
       </c>
     </row>
     <row r="38">
@@ -913,7 +913,7 @@
         <v>0.007</v>
       </c>
       <c r="B38" t="n">
-        <v>8.191986499258075</v>
+        <v>8.259128242207483</v>
       </c>
     </row>
     <row r="39">
@@ -921,7 +921,7 @@
         <v>0.0042</v>
       </c>
       <c r="B39" t="n">
-        <v>8.189133967719497</v>
+        <v>8.25912823280755</v>
       </c>
     </row>
     <row r="40">
@@ -929,7 +929,7 @@
         <v>0.0014</v>
       </c>
       <c r="B40" t="n">
-        <v>8.192370324294622</v>
+        <v>8.259128184006039</v>
       </c>
     </row>
     <row r="41">
@@ -937,7 +937,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B41" t="n">
-        <v>8.188708512347855</v>
+        <v>8.259127930643936</v>
       </c>
     </row>
     <row r="42">
@@ -945,7 +945,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B42" t="n">
-        <v>8.182470105518634</v>
+        <v>8.25912661526973</v>
       </c>
     </row>
     <row r="43">
@@ -953,7 +953,7 @@
         <v>-0.007</v>
       </c>
       <c r="B43" t="n">
-        <v>8.180201707416495</v>
+        <v>8.259119786330338</v>
       </c>
     </row>
     <row r="44">
@@ -961,7 +961,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B44" t="n">
-        <v>8.170769637729297</v>
+        <v>8.259084334568529</v>
       </c>
     </row>
     <row r="45">
@@ -969,7 +969,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B45" t="n">
-        <v>8.261370299826801</v>
+        <v>8.258900332872011</v>
       </c>
     </row>
     <row r="46">
@@ -977,7 +977,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B46" t="n">
-        <v>8.436582548855364</v>
+        <v>8.257946473921889</v>
       </c>
     </row>
     <row r="47">
@@ -985,7 +985,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B47" t="n">
-        <v>8.563203879004737</v>
+        <v>8.253032318066834</v>
       </c>
     </row>
     <row r="48">
@@ -993,7 +993,7 @@
         <v>-0.021</v>
       </c>
       <c r="B48" t="n">
-        <v>8.612640344994293</v>
+        <v>8.228502630534503</v>
       </c>
     </row>
     <row r="49">
@@ -1001,7 +1001,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B49" t="n">
-        <v>8.397341929105288</v>
+        <v>8.122969002213864</v>
       </c>
     </row>
     <row r="50">
@@ -1009,7 +1009,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B50" t="n">
-        <v>8.187604339112557</v>
+        <v>7.854206626126825</v>
       </c>
     </row>
     <row r="51">
@@ -1017,7 +1017,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B51" t="n">
-        <v>8.709972511140437</v>
+        <v>7.605817491769306</v>
       </c>
     </row>
     <row r="52">
@@ -1025,7 +1025,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B52" t="n">
-        <v>9.215041836348</v>
+        <v>7.51828269040557</v>
       </c>
     </row>
     <row r="53">
@@ -1033,7 +1033,7 @@
         <v>-0.035</v>
       </c>
       <c r="B53" t="n">
-        <v>9.338333271919506</v>
+        <v>7.498656525030412</v>
       </c>
     </row>
   </sheetData>
@@ -1074,11 +1074,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>模型生成（非实测）</t>
+          <t>标准双支路模型生成（非实测）</t>
         </is>
       </c>
     </row>
@@ -1149,55 +1149,67 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.7653084889（保持前次角度模型）</t>
+          <t>0.7653084889</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>曲线形状</t>
+          <t>开关阈值Ic</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>角度相关形状模板：0°/45°/75°实测回线归一化后按角度混合</t>
+          <t>±0.02640192 A（平滑角度模型）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>形状插值</t>
+          <t>开关宽度</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0°→45°线性混合</t>
+          <t>0.00170000 A（窄开关区）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>纵轴单位</t>
+          <t>曲线结构</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>原始文件未注明，保留原始数值尺度</t>
+          <t>支路1在+Ic由低平台翻到高平台；支路2在−Ic由高平台翻到低平台</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>噪声处理</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>未添加随机噪声；未使用原始回线端点噪声</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>实测区分</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>本文件为模型生成数据；15°、30°、60°无原始OPJU，0°/45°为统一点数并按实测模板生成</t>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>本文件是模型预测/标准化数据，不是该角度的原始实测记录</t>
         </is>
       </c>
     </row>
